--- a/test/ifa/resumifa.txt.xlsx
+++ b/test/ifa/resumifa.txt.xlsx
@@ -249,11 +249,12 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -275,29 +276,42 @@
       <sz val="11"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="13"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
       <sz val="12"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <i val="true"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFC9211E"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -378,7 +392,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -391,19 +405,15 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -411,23 +421,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -435,23 +445,31 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -459,15 +477,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -553,7 +571,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:G75"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.94"/>
@@ -684,7 +702,7 @@
       <c r="C33" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="D33" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E33" s="0" t="s">
@@ -698,520 +716,520 @@
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="4" t="s">
+      <c r="A34" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="D34" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="8" t="n">
+      <c r="E34" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="9" t="n">
+      <c r="F34" s="8" t="n">
         <v>9</v>
       </c>
-      <c r="G34" s="9" t="n">
+      <c r="G34" s="8" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="4"/>
-      <c r="B35" s="5"/>
-      <c r="C35" s="6"/>
-      <c r="D35" s="7" t="s">
+      <c r="A35" s="3"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="5"/>
+      <c r="D35" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E35" s="8"/>
-      <c r="F35" s="9"/>
-      <c r="G35" s="9"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="4"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="6" t="s">
+      <c r="A36" s="3"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D36" s="7" t="s">
+      <c r="D36" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E36" s="10" t="n">
+      <c r="E36" s="9" t="n">
         <f aca="false">E34+1</f>
         <v>2</v>
       </c>
-      <c r="F36" s="9" t="n">
+      <c r="F36" s="8" t="n">
         <v>10</v>
       </c>
-      <c r="G36" s="9" t="n">
+      <c r="G36" s="8" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="4"/>
-      <c r="B37" s="5"/>
-      <c r="C37" s="6"/>
-      <c r="D37" s="7" t="s">
+      <c r="A37" s="3"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E37" s="10"/>
-      <c r="F37" s="9"/>
-      <c r="G37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="4"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="7" t="s">
+      <c r="A38" s="3"/>
+      <c r="B38" s="4"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E38" s="10"/>
-      <c r="F38" s="9"/>
-      <c r="G38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="4"/>
-      <c r="B39" s="11" t="s">
+      <c r="A39" s="3"/>
+      <c r="B39" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="C39" s="12" t="s">
+      <c r="C39" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="E39" s="10" t="n">
+      <c r="E39" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="F39" s="9" t="n">
+      <c r="F39" s="8" t="n">
         <v>11</v>
       </c>
-      <c r="G39" s="9" t="n">
+      <c r="G39" s="8" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="4"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="13" t="s">
+      <c r="A40" s="3"/>
+      <c r="B40" s="10"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="E40" s="10"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="4"/>
-      <c r="B41" s="11"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="13" t="s">
+      <c r="A41" s="3"/>
+      <c r="B41" s="10"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E41" s="10"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8"/>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="4"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="12" t="s">
+      <c r="A42" s="3"/>
+      <c r="B42" s="10"/>
+      <c r="C42" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="E42" s="10" t="n">
+      <c r="E42" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="F42" s="14" t="s">
+      <c r="F42" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="G42" s="9" t="n">
+      <c r="G42" s="8" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="4"/>
-      <c r="B43" s="11"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="13" t="s">
+      <c r="A43" s="3"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E43" s="10"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="8"/>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="4"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="13" t="s">
+      <c r="A44" s="3"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="E44" s="10"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="8"/>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="4"/>
-      <c r="B45" s="11"/>
-      <c r="C45" s="12" t="s">
+      <c r="A45" s="3"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="E45" s="10" t="n">
+      <c r="E45" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="F45" s="15" t="s">
+      <c r="F45" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="G45" s="16" t="n">
+      <c r="G45" s="17" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="13" t="s">
+      <c r="A46" s="3"/>
+      <c r="B46" s="10"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E46" s="10"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="16"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="17"/>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="4"/>
-      <c r="B47" s="11"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="13" t="s">
+      <c r="A47" s="3"/>
+      <c r="B47" s="10"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E47" s="10"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="16"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="17"/>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="4"/>
-      <c r="B48" s="17" t="s">
+      <c r="A48" s="3"/>
+      <c r="B48" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="C48" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D48" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E48" s="10" t="n">
+      <c r="E48" s="9" t="n">
         <v>6</v>
       </c>
-      <c r="F48" s="15" t="s">
+      <c r="F48" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="G48" s="16" t="n">
+      <c r="G48" s="17" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="4"/>
-      <c r="B49" s="17"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="19" t="s">
+      <c r="A49" s="3"/>
+      <c r="B49" s="18"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="E49" s="10"/>
-      <c r="F49" s="15"/>
-      <c r="G49" s="16"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="16"/>
+      <c r="G49" s="17"/>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="4"/>
-      <c r="B50" s="17"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="19" t="s">
+      <c r="A50" s="3"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E50" s="10"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="16"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="16"/>
+      <c r="G50" s="17"/>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="4"/>
-      <c r="B51" s="17"/>
-      <c r="C51" s="18" t="s">
+      <c r="A51" s="3"/>
+      <c r="B51" s="18"/>
+      <c r="C51" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D51" s="19" t="s">
+      <c r="D51" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E51" s="10" t="n">
+      <c r="E51" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="F51" s="15" t="s">
+      <c r="F51" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="G51" s="16" t="n">
+      <c r="G51" s="17" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="4"/>
-      <c r="B52" s="17"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="19" t="s">
+      <c r="A52" s="3"/>
+      <c r="B52" s="18"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="E52" s="10"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="16"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="17"/>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="4"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="19" t="s">
+      <c r="A53" s="3"/>
+      <c r="B53" s="18"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="E53" s="10"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="16"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="16"/>
+      <c r="G53" s="17"/>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="4"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="18" t="s">
+      <c r="A54" s="3"/>
+      <c r="B54" s="18"/>
+      <c r="C54" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D54" s="20" t="s">
+      <c r="D54" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="E54" s="10" t="n">
+      <c r="E54" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="F54" s="15" t="s">
+      <c r="F54" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="G54" s="16" t="n">
+      <c r="G54" s="17" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="4"/>
-      <c r="B55" s="17"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="20" t="s">
+      <c r="A55" s="3"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="E55" s="10"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="16"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="17"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="4"/>
-      <c r="B56" s="17"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="20" t="s">
+      <c r="A56" s="3"/>
+      <c r="B56" s="18"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E56" s="10"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="16"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="16"/>
+      <c r="G56" s="17"/>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="4"/>
-      <c r="B57" s="21" t="s">
+      <c r="A57" s="3"/>
+      <c r="B57" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="C57" s="22" t="s">
+      <c r="C57" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="D57" s="23" t="s">
+      <c r="D57" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="E57" s="8" t="n">
+      <c r="E57" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="F57" s="9"/>
-      <c r="G57" s="9" t="n">
+      <c r="F57" s="8"/>
+      <c r="G57" s="8" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="4"/>
-      <c r="B58" s="21"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="23" t="s">
+      <c r="A58" s="3"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="23"/>
+      <c r="D58" s="24" t="s">
         <v>57</v>
       </c>
-      <c r="E58" s="8"/>
-      <c r="F58" s="9"/>
-      <c r="G58" s="9"/>
+      <c r="E58" s="7"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="4"/>
-      <c r="B59" s="21"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="23" t="s">
+      <c r="A59" s="3"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="23"/>
+      <c r="D59" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="E59" s="8"/>
-      <c r="F59" s="9"/>
-      <c r="G59" s="9"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="4"/>
-      <c r="B60" s="21"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="23" t="s">
+      <c r="A60" s="3"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="23"/>
+      <c r="D60" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="E60" s="8"/>
-      <c r="F60" s="9"/>
-      <c r="G60" s="9"/>
+      <c r="E60" s="7"/>
+      <c r="F60" s="8"/>
+      <c r="G60" s="8"/>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="4"/>
-      <c r="B61" s="21"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="23" t="s">
+      <c r="A61" s="3"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="23"/>
+      <c r="D61" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="E61" s="8"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="8"/>
+      <c r="G61" s="8"/>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="4"/>
-      <c r="B62" s="21"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="23" t="s">
+      <c r="A62" s="3"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="23"/>
+      <c r="D62" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="E62" s="8"/>
-      <c r="F62" s="9"/>
-      <c r="G62" s="9"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="8"/>
+      <c r="G62" s="8"/>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="4"/>
-      <c r="B63" s="21"/>
-      <c r="C63" s="22"/>
-      <c r="D63" s="23" t="s">
+      <c r="A63" s="3"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="23"/>
+      <c r="D63" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="E63" s="8"/>
-      <c r="F63" s="9"/>
-      <c r="G63" s="9"/>
+      <c r="E63" s="7"/>
+      <c r="F63" s="8"/>
+      <c r="G63" s="8"/>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="4"/>
-      <c r="B64" s="21"/>
-      <c r="C64" s="22"/>
-      <c r="D64" s="23" t="s">
+      <c r="A64" s="3"/>
+      <c r="B64" s="22"/>
+      <c r="C64" s="23"/>
+      <c r="D64" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="E64" s="8"/>
-      <c r="F64" s="9"/>
-      <c r="G64" s="9"/>
+      <c r="E64" s="7"/>
+      <c r="F64" s="8"/>
+      <c r="G64" s="8"/>
     </row>
     <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="4"/>
-      <c r="B65" s="21"/>
-      <c r="C65" s="22" t="s">
+      <c r="A65" s="3"/>
+      <c r="B65" s="22"/>
+      <c r="C65" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="D65" s="23" t="s">
+      <c r="D65" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="E65" s="8" t="n">
+      <c r="E65" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9" t="n">
+      <c r="F65" s="8"/>
+      <c r="G65" s="8" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="4"/>
-      <c r="B66" s="21"/>
-      <c r="C66" s="22"/>
-      <c r="D66" s="23" t="s">
+      <c r="A66" s="3"/>
+      <c r="B66" s="22"/>
+      <c r="C66" s="23"/>
+      <c r="D66" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="E66" s="8"/>
-      <c r="F66" s="9"/>
-      <c r="G66" s="9"/>
+      <c r="E66" s="7"/>
+      <c r="F66" s="8"/>
+      <c r="G66" s="8"/>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="4"/>
-      <c r="B67" s="21"/>
-      <c r="C67" s="22"/>
-      <c r="D67" s="23" t="s">
+      <c r="A67" s="3"/>
+      <c r="B67" s="22"/>
+      <c r="C67" s="23"/>
+      <c r="D67" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="E67" s="8"/>
-      <c r="F67" s="9"/>
-      <c r="G67" s="9"/>
+      <c r="E67" s="7"/>
+      <c r="F67" s="8"/>
+      <c r="G67" s="8"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="4"/>
-      <c r="B68" s="21"/>
-      <c r="C68" s="22"/>
-      <c r="D68" s="23" t="s">
+      <c r="A68" s="3"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="23"/>
+      <c r="D68" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="E68" s="8"/>
-      <c r="F68" s="9"/>
-      <c r="G68" s="9"/>
+      <c r="E68" s="7"/>
+      <c r="F68" s="8"/>
+      <c r="G68" s="8"/>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="4"/>
-      <c r="B69" s="21"/>
-      <c r="C69" s="22"/>
-      <c r="D69" s="23" t="s">
+      <c r="A69" s="3"/>
+      <c r="B69" s="22"/>
+      <c r="C69" s="23"/>
+      <c r="D69" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="E69" s="8"/>
-      <c r="F69" s="9"/>
-      <c r="G69" s="9"/>
+      <c r="E69" s="7"/>
+      <c r="F69" s="8"/>
+      <c r="G69" s="8"/>
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="4"/>
-      <c r="B70" s="21"/>
-      <c r="C70" s="22"/>
-      <c r="D70" s="23" t="s">
+      <c r="A70" s="3"/>
+      <c r="B70" s="22"/>
+      <c r="C70" s="23"/>
+      <c r="D70" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="E70" s="8"/>
-      <c r="F70" s="9"/>
-      <c r="G70" s="9"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="4"/>
-      <c r="B71" s="21"/>
-      <c r="C71" s="22"/>
-      <c r="D71" s="23" t="s">
+      <c r="A71" s="3"/>
+      <c r="B71" s="22"/>
+      <c r="C71" s="23"/>
+      <c r="D71" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="E71" s="8"/>
-      <c r="F71" s="9"/>
-      <c r="G71" s="9"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="8"/>
+      <c r="G71" s="8"/>
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="4"/>
-      <c r="B72" s="21"/>
-      <c r="C72" s="22"/>
-      <c r="D72" s="23" t="s">
+      <c r="A72" s="3"/>
+      <c r="B72" s="22"/>
+      <c r="C72" s="23"/>
+      <c r="D72" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="E72" s="8"/>
-      <c r="F72" s="9"/>
-      <c r="G72" s="9"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="8"/>
+      <c r="G72" s="8"/>
     </row>
     <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">

--- a/test/ifa/resumifa.txt.xlsx
+++ b/test/ifa/resumifa.txt.xlsx
@@ -571,7 +571,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:G75"/>
-  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.94"/>

--- a/test/ifa/resumifa.txt.xlsx
+++ b/test/ifa/resumifa.txt.xlsx
@@ -571,7 +571,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A2:G75"/>
-  <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.58984375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.94"/>
